--- a/templates/21-cause-effect-fishbone.xlsx
+++ b/templates/21-cause-effect-fishbone.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="How to use this" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Fishbone" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Category prompts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Fishbone diagram" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Category prompts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,10 +52,18 @@
       <sz val="11"/>
     </font>
     <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -91,8 +100,13 @@
         <fgColor rgb="FFF2F7FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0392B"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -114,16 +128,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalDown="1">
+      <diagonal style="medium">
+        <color rgb="FF333C49"/>
+      </diagonal>
+    </border>
+    <border diagonalUp="1">
+      <diagonal style="medium">
+        <color rgb="FF333C49"/>
+      </diagonal>
+    </border>
+    <border>
+      <bottom style="thick">
+        <color rgb="FF151B24"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -148,6 +177,20 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -775,7 +818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:T46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -784,6 +827,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
+    <col hidden="1" width="22" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -862,6 +906,11 @@
           <t>Evidence you would need</t>
         </is>
       </c>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>key (used by the diagram)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -889,94 +938,258 @@
           <t>Reopens where closure timestamp precedes the posting webhook</t>
         </is>
       </c>
+      <c r="T8" s="5">
+        <f>IF(A8="","",A8&amp;"|"&amp;COUNTIF($A$8:A8,A8))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="n"/>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="13" t="n"/>
-      <c r="E9" s="14">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Billing Ops pull the queue once a day, so nothing moves overnight</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="12">
         <f>IF(COUNT(C9:D9)&lt;2,"",C9*D9)</f>
         <v/>
       </c>
-      <c r="F9" s="13" t="n"/>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>Queue age distribution by hour of arrival</t>
+        </is>
+      </c>
+      <c r="T9" s="5">
+        <f>IF(A9="","",A9&amp;"|"&amp;COUNTIF($A$8:A9,A9))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="n"/>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="14">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Systems</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>The status model has no pending-adjustment state</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="12">
         <f>IF(COUNT(C10:D10)&lt;2,"",C10*D10)</f>
         <v/>
       </c>
-      <c r="F10" s="13" t="n"/>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>Count of closures with an adjustment still in flight</t>
+        </is>
+      </c>
+      <c r="T10" s="5">
+        <f>IF(A10="","",A10&amp;"|"&amp;COUNTIF($A$8:A10,A10))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="n"/>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="14">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Systems</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>The nightly adjustment batch fails silently</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" s="12">
         <f>IF(COUNT(C11:D11)&lt;2,"",C11*D11)</f>
         <v/>
       </c>
-      <c r="F11" s="13" t="n"/>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>Batch exit codes against the days reopens spiked</t>
+        </is>
+      </c>
+      <c r="T11" s="5">
+        <f>IF(A11="","",A11&amp;"|"&amp;COUNTIF($A$8:A11,A11))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="n"/>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="14">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>New hires close on the request, not on the posting</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="12">
         <f>IF(COUNT(C12:D12)&lt;2,"",C12*D12)</f>
         <v/>
       </c>
-      <c r="F12" s="13" t="n"/>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Reopen rate split by agent tenure band</t>
+        </is>
+      </c>
+      <c r="T12" s="5">
+        <f>IF(A12="","",A12&amp;"|"&amp;COUNTIF($A$8:A12,A12))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="n"/>
-      <c r="B13" s="13" t="n"/>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="13" t="n"/>
-      <c r="E13" s="14">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Knowledge</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>No written definition of 'resolved' for a billing adjustment</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="12">
         <f>IF(COUNT(C13:D13)&lt;2,"",C13*D13)</f>
         <v/>
       </c>
-      <c r="F13" s="13" t="n"/>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>Ask ten agents to define it and compare the answers</t>
+        </is>
+      </c>
+      <c r="T13" s="5">
+        <f>IF(A13="","",A13&amp;"|"&amp;COUNTIF($A$8:A13,A13))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="n"/>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Routing &amp; demand</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Adjustment requests route to general billing, not the adjustments desk</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="12">
         <f>IF(COUNT(C14:D14)&lt;2,"",C14*D14)</f>
         <v/>
       </c>
-      <c r="F14" s="13" t="n"/>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>Share of reopens that were transferred at least once</t>
+        </is>
+      </c>
+      <c r="T14" s="5">
+        <f>IF(A14="","",A14&amp;"|"&amp;COUNTIF($A$8:A14,A14))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="n"/>
-      <c r="B15" s="13" t="n"/>
-      <c r="C15" s="13" t="n"/>
-      <c r="D15" s="13" t="n"/>
-      <c r="E15" s="14">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Product / upstream</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>The billing platform posts asynchronously with no callback</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" s="12">
         <f>IF(COUNT(C15:D15)&lt;2,"",C15*D15)</f>
         <v/>
       </c>
-      <c r="F15" s="13" t="n"/>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Distribution of the gap between request and posting</t>
+        </is>
+      </c>
+      <c r="T15" s="5">
+        <f>IF(A15="","",A15&amp;"|"&amp;COUNTIF($A$8:A15,A15))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="n"/>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="14">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Measurement</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Reopen rate counts same-reason reopens only, hiding the rest</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" s="12">
         <f>IF(COUNT(C16:D16)&lt;2,"",C16*D16)</f>
         <v/>
       </c>
-      <c r="F16" s="13" t="n"/>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>Recount on an any-reason definition</t>
+        </is>
+      </c>
+      <c r="T16" s="5">
+        <f>IF(A16="","",A16&amp;"|"&amp;COUNTIF($A$8:A16,A16))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="n"/>
@@ -988,6 +1201,10 @@
         <v/>
       </c>
       <c r="F17" s="13" t="n"/>
+      <c r="T17" s="5">
+        <f>IF(A17="","",A17&amp;"|"&amp;COUNTIF($A$8:A17,A17))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="n"/>
@@ -999,6 +1216,10 @@
         <v/>
       </c>
       <c r="F18" s="13" t="n"/>
+      <c r="T18" s="5">
+        <f>IF(A18="","",A18&amp;"|"&amp;COUNTIF($A$8:A18,A18))</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="n"/>
@@ -1010,6 +1231,10 @@
         <v/>
       </c>
       <c r="F19" s="13" t="n"/>
+      <c r="T19" s="5">
+        <f>IF(A19="","",A19&amp;"|"&amp;COUNTIF($A$8:A19,A19))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="n"/>
@@ -1021,6 +1246,10 @@
         <v/>
       </c>
       <c r="F20" s="13" t="n"/>
+      <c r="T20" s="5">
+        <f>IF(A20="","",A20&amp;"|"&amp;COUNTIF($A$8:A20,A20))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="n"/>
@@ -1032,6 +1261,10 @@
         <v/>
       </c>
       <c r="F21" s="13" t="n"/>
+      <c r="T21" s="5">
+        <f>IF(A21="","",A21&amp;"|"&amp;COUNTIF($A$8:A21,A21))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="n"/>
@@ -1043,6 +1276,10 @@
         <v/>
       </c>
       <c r="F22" s="13" t="n"/>
+      <c r="T22" s="5">
+        <f>IF(A22="","",A22&amp;"|"&amp;COUNTIF($A$8:A22,A22))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="n"/>
@@ -1054,6 +1291,10 @@
         <v/>
       </c>
       <c r="F23" s="13" t="n"/>
+      <c r="T23" s="5">
+        <f>IF(A23="","",A23&amp;"|"&amp;COUNTIF($A$8:A23,A23))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="n"/>
@@ -1065,6 +1306,10 @@
         <v/>
       </c>
       <c r="F24" s="13" t="n"/>
+      <c r="T24" s="5">
+        <f>IF(A24="","",A24&amp;"|"&amp;COUNTIF($A$8:A24,A24))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="n"/>
@@ -1076,6 +1321,10 @@
         <v/>
       </c>
       <c r="F25" s="13" t="n"/>
+      <c r="T25" s="5">
+        <f>IF(A25="","",A25&amp;"|"&amp;COUNTIF($A$8:A25,A25))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="n"/>
@@ -1087,6 +1336,10 @@
         <v/>
       </c>
       <c r="F26" s="13" t="n"/>
+      <c r="T26" s="5">
+        <f>IF(A26="","",A26&amp;"|"&amp;COUNTIF($A$8:A26,A26))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="n"/>
@@ -1098,6 +1351,10 @@
         <v/>
       </c>
       <c r="F27" s="13" t="n"/>
+      <c r="T27" s="5">
+        <f>IF(A27="","",A27&amp;"|"&amp;COUNTIF($A$8:A27,A27))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="n"/>
@@ -1109,6 +1366,10 @@
         <v/>
       </c>
       <c r="F28" s="13" t="n"/>
+      <c r="T28" s="5">
+        <f>IF(A28="","",A28&amp;"|"&amp;COUNTIF($A$8:A28,A28))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="n"/>
@@ -1120,6 +1381,10 @@
         <v/>
       </c>
       <c r="F29" s="13" t="n"/>
+      <c r="T29" s="5">
+        <f>IF(A29="","",A29&amp;"|"&amp;COUNTIF($A$8:A29,A29))</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="n"/>
@@ -1131,6 +1396,10 @@
         <v/>
       </c>
       <c r="F30" s="13" t="n"/>
+      <c r="T30" s="5">
+        <f>IF(A30="","",A30&amp;"|"&amp;COUNTIF($A$8:A30,A30))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="13" t="n"/>
@@ -1142,6 +1411,10 @@
         <v/>
       </c>
       <c r="F31" s="13" t="n"/>
+      <c r="T31" s="5">
+        <f>IF(A31="","",A31&amp;"|"&amp;COUNTIF($A$8:A31,A31))</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="n"/>
@@ -1153,6 +1426,10 @@
         <v/>
       </c>
       <c r="F32" s="13" t="n"/>
+      <c r="T32" s="5">
+        <f>IF(A32="","",A32&amp;"|"&amp;COUNTIF($A$8:A32,A32))</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="13" t="n"/>
@@ -1164,6 +1441,10 @@
         <v/>
       </c>
       <c r="F33" s="13" t="n"/>
+      <c r="T33" s="5">
+        <f>IF(A33="","",A33&amp;"|"&amp;COUNTIF($A$8:A33,A33))</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="13" t="n"/>
@@ -1175,6 +1456,10 @@
         <v/>
       </c>
       <c r="F34" s="13" t="n"/>
+      <c r="T34" s="5">
+        <f>IF(A34="","",A34&amp;"|"&amp;COUNTIF($A$8:A34,A34))</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="13" t="n"/>
@@ -1186,6 +1471,10 @@
         <v/>
       </c>
       <c r="F35" s="13" t="n"/>
+      <c r="T35" s="5">
+        <f>IF(A35="","",A35&amp;"|"&amp;COUNTIF($A$8:A35,A35))</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -1370,6 +1659,423 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:AD28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="7.5" customWidth="1" min="2" max="2"/>
+    <col width="7.5" customWidth="1" min="3" max="3"/>
+    <col width="7.5" customWidth="1" min="4" max="4"/>
+    <col width="7.5" customWidth="1" min="5" max="5"/>
+    <col width="7.5" customWidth="1" min="6" max="6"/>
+    <col width="7.5" customWidth="1" min="7" max="7"/>
+    <col width="7.5" customWidth="1" min="8" max="8"/>
+    <col width="7.5" customWidth="1" min="9" max="9"/>
+    <col width="7.5" customWidth="1" min="10" max="10"/>
+    <col width="7.5" customWidth="1" min="11" max="11"/>
+    <col width="7.5" customWidth="1" min="12" max="12"/>
+    <col width="7.5" customWidth="1" min="13" max="13"/>
+    <col width="7.5" customWidth="1" min="14" max="14"/>
+    <col width="7.5" customWidth="1" min="15" max="15"/>
+    <col width="7.5" customWidth="1" min="16" max="16"/>
+    <col width="7.5" customWidth="1" min="17" max="17"/>
+    <col width="7.5" customWidth="1" min="18" max="18"/>
+    <col width="7.5" customWidth="1" min="19" max="19"/>
+    <col width="7.5" customWidth="1" min="20" max="20"/>
+    <col width="7.5" customWidth="1" min="21" max="21"/>
+    <col width="7.5" customWidth="1" min="22" max="22"/>
+    <col width="7.5" customWidth="1" min="23" max="23"/>
+    <col width="7.5" customWidth="1" min="24" max="24"/>
+    <col width="7.5" customWidth="1" min="25" max="25"/>
+    <col width="7.5" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Cause &amp; effect — the diagram</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
+      <c r="H1" s="4" t="n"/>
+      <c r="I1" s="4" t="n"/>
+      <c r="J1" s="4" t="n"/>
+      <c r="K1" s="4" t="n"/>
+      <c r="L1" s="4" t="n"/>
+      <c r="M1" s="4" t="n"/>
+      <c r="N1" s="4" t="n"/>
+      <c r="O1" s="4" t="n"/>
+      <c r="P1" s="4" t="n"/>
+      <c r="Q1" s="4" t="n"/>
+      <c r="R1" s="4" t="n"/>
+      <c r="S1" s="4" t="n"/>
+      <c r="T1" s="4" t="n"/>
+      <c r="U1" s="4" t="n"/>
+      <c r="V1" s="4" t="n"/>
+      <c r="W1" s="4" t="n"/>
+      <c r="X1" s="4" t="n"/>
+      <c r="Y1" s="4" t="n"/>
+      <c r="Z1" s="4" t="n"/>
+      <c r="AA1" s="4" t="n"/>
+      <c r="AB1" s="4" t="n"/>
+      <c r="AC1" s="4" t="n"/>
+      <c r="AD1" s="4" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Every box below is a formula reading the Fishbone tab. Type there; this redraws itself. Four causes per branch are shown — the tab holds as many as you like.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="20" customHeight="1">
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="n"/>
+      <c r="D4" s="18" t="n"/>
+      <c r="E4" s="18" t="n"/>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="I4" s="18" t="n"/>
+      <c r="J4" s="18" t="n"/>
+      <c r="K4" s="18" t="n"/>
+      <c r="N4" s="17" t="inlineStr">
+        <is>
+          <t>Systems</t>
+        </is>
+      </c>
+      <c r="O4" s="18" t="n"/>
+      <c r="P4" s="18" t="n"/>
+      <c r="Q4" s="18" t="n"/>
+      <c r="T4" s="17" t="inlineStr">
+        <is>
+          <t>Knowledge</t>
+        </is>
+      </c>
+      <c r="U4" s="18" t="n"/>
+      <c r="V4" s="18" t="n"/>
+      <c r="W4" s="18" t="n"/>
+    </row>
+    <row r="5">
+      <c r="F5" s="19" t="n"/>
+      <c r="L5" s="19" t="n"/>
+      <c r="R5" s="19" t="n"/>
+      <c r="X5" s="19" t="n"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="B6" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("People|1",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Process|1",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N6" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Systems|1",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+      <c r="T6" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Knowledge|1",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="26" customHeight="1">
+      <c r="B8" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("People|2",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Process|2",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N8" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Systems|2",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+      <c r="T8" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Knowledge|2",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="26" customHeight="1">
+      <c r="B10" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("People|3",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Process|3",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N10" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Systems|3",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+      <c r="T10" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Knowledge|3",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12" ht="26" customHeight="1">
+      <c r="B12" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("People|4",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Process|4",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N12" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Systems|4",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+      <c r="T12" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Knowledge|4",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+      <c r="AA12" s="21">
+        <f>Fishbone!B5</f>
+        <v/>
+      </c>
+      <c r="AB12" s="22" t="n"/>
+      <c r="AC12" s="22" t="n"/>
+      <c r="AD12" s="22" t="n"/>
+    </row>
+    <row r="13">
+      <c r="AA13" s="22" t="n"/>
+      <c r="AB13" s="22" t="n"/>
+      <c r="AC13" s="22" t="n"/>
+      <c r="AD13" s="22" t="n"/>
+    </row>
+    <row r="14">
+      <c r="AA14" s="22" t="n"/>
+      <c r="AB14" s="22" t="n"/>
+      <c r="AC14" s="22" t="n"/>
+      <c r="AD14" s="22" t="n"/>
+    </row>
+    <row r="15" ht="10" customHeight="1">
+      <c r="B15" s="23" t="n"/>
+      <c r="C15" s="23" t="n"/>
+      <c r="D15" s="23" t="n"/>
+      <c r="E15" s="23" t="n"/>
+      <c r="F15" s="23" t="n"/>
+      <c r="G15" s="23" t="n"/>
+      <c r="H15" s="23" t="n"/>
+      <c r="I15" s="23" t="n"/>
+      <c r="J15" s="23" t="n"/>
+      <c r="K15" s="23" t="n"/>
+      <c r="L15" s="23" t="n"/>
+      <c r="M15" s="23" t="n"/>
+      <c r="N15" s="23" t="n"/>
+      <c r="O15" s="23" t="n"/>
+      <c r="P15" s="23" t="n"/>
+      <c r="Q15" s="23" t="n"/>
+      <c r="R15" s="23" t="n"/>
+      <c r="S15" s="23" t="n"/>
+      <c r="T15" s="23" t="n"/>
+      <c r="U15" s="23" t="n"/>
+      <c r="V15" s="23" t="n"/>
+      <c r="W15" s="23" t="n"/>
+      <c r="X15" s="23" t="n"/>
+      <c r="Y15" s="23" t="n"/>
+      <c r="Z15" s="23" t="n"/>
+      <c r="AA15" s="22" t="n"/>
+      <c r="AB15" s="22" t="n"/>
+      <c r="AC15" s="22" t="n"/>
+      <c r="AD15" s="22" t="n"/>
+    </row>
+    <row r="16">
+      <c r="I16" s="24" t="n"/>
+      <c r="O16" s="24" t="n"/>
+      <c r="U16" s="24" t="n"/>
+      <c r="AA16" s="22" t="n"/>
+      <c r="AB16" s="22" t="n"/>
+      <c r="AC16" s="22" t="n"/>
+      <c r="AD16" s="22" t="n"/>
+    </row>
+    <row r="17">
+      <c r="AA17" s="22" t="n"/>
+      <c r="AB17" s="22" t="n"/>
+      <c r="AC17" s="22" t="n"/>
+      <c r="AD17" s="22" t="n"/>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="E18" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Routing &amp; demand|1",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+      <c r="K18" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Product / upstream|1",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Q18" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Measurement|1",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+      <c r="AA18" s="22" t="n"/>
+      <c r="AB18" s="22" t="n"/>
+      <c r="AC18" s="22" t="n"/>
+      <c r="AD18" s="22" t="n"/>
+    </row>
+    <row r="19"/>
+    <row r="20" ht="26" customHeight="1">
+      <c r="E20" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Routing &amp; demand|2",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+      <c r="K20" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Product / upstream|2",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Q20" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Measurement|2",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22" ht="26" customHeight="1">
+      <c r="E22" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Routing &amp; demand|3",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+      <c r="K22" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Product / upstream|3",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Q22" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Measurement|3",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24" ht="26" customHeight="1">
+      <c r="E24" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Routing &amp; demand|4",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+      <c r="K24" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Product / upstream|4",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Q24" s="20">
+        <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Measurement|4",Fishbone!$T$8:$T$35,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26" ht="20" customHeight="1">
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>Routing &amp; demand</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="n"/>
+      <c r="G26" s="18" t="n"/>
+      <c r="H26" s="18" t="n"/>
+      <c r="K26" s="17" t="inlineStr">
+        <is>
+          <t>Product / upstream</t>
+        </is>
+      </c>
+      <c r="L26" s="18" t="n"/>
+      <c r="M26" s="18" t="n"/>
+      <c r="N26" s="18" t="n"/>
+      <c r="Q26" s="17" t="inlineStr">
+        <is>
+          <t>Measurement</t>
+        </is>
+      </c>
+      <c r="R26" s="18" t="n"/>
+      <c r="S26" s="18" t="n"/>
+      <c r="T26" s="18" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>A branch with no boxes is where you are not looking, not where there is nothing to find. An empty Measurement branch is almost always wrong.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="46">
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="T8:W8"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="H12:K12"/>
+    <mergeCell ref="N6:Q6"/>
+    <mergeCell ref="T6:W6"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="I16:J25"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="K18:N18"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="F5:G14"/>
+    <mergeCell ref="H8:K8"/>
+    <mergeCell ref="U16:V25"/>
+    <mergeCell ref="L5:M14"/>
+    <mergeCell ref="N4:Q4"/>
+    <mergeCell ref="A2:AD2"/>
+    <mergeCell ref="AA12:AD18"/>
+    <mergeCell ref="K24:N24"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="H10:K10"/>
+    <mergeCell ref="O16:P25"/>
+    <mergeCell ref="Q24:T24"/>
+    <mergeCell ref="Q18:T18"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="T4:W4"/>
+    <mergeCell ref="X5:Y14"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="K20:N20"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="T10:W10"/>
+    <mergeCell ref="N12:Q12"/>
+    <mergeCell ref="A28:AD28"/>
+    <mergeCell ref="Q20:T20"/>
+    <mergeCell ref="Q26:T26"/>
+    <mergeCell ref="R5:S14"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="K22:N22"/>
+    <mergeCell ref="N8:Q8"/>
+    <mergeCell ref="T12:W12"/>
+    <mergeCell ref="Q22:T22"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="N10:Q10"/>
+    <mergeCell ref="A1:AD1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1399,7 +2105,7 @@
           <t>People</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Skill, tenure, authority limits, coaching, workload, incentive conflicts.</t>
         </is>
@@ -1411,7 +2117,7 @@
           <t>Process</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Steps that can be skipped, missing pending states, approvals, handoffs, queue discipline.</t>
         </is>
@@ -1423,7 +2129,7 @@
           <t>Systems</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Tooling gaps, swivel-chair work, latency, permissions, integrations that fail silently.</t>
         </is>
@@ -1435,7 +2141,7 @@
           <t>Knowledge</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Missing or wrong articles, search that does not find them, content nobody owns.</t>
         </is>
@@ -1447,7 +2153,7 @@
           <t>Routing &amp; demand</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Mis-routing, IVR options, skill-based routing rules, arrival patterns, mix shift.</t>
         </is>
@@ -1459,7 +2165,7 @@
           <t>Product / upstream</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Defects reaching customers, confusing UX, billing logic, release cadence.</t>
         </is>
@@ -1471,7 +2177,7 @@
           <t>Measurement</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Disposition codes, QA rubric, operational definitions, instrumentation gaps.</t>
         </is>

--- a/templates/21-cause-effect-fishbone.xlsx
+++ b/templates/21-cause-effect-fishbone.xlsx
@@ -352,6 +352,21 @@
 </chartSpace>
 </file>
 
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Template</author>
+  </authors>
+  <commentList>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <t>Copy the problem statement's metric and magnitude verbatim — the measured value, the target, and the population. A vague effect gives you a fishbone of vague causes.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -1650,6 +1665,7 @@
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/templates/21-cause-effect-fishbone.xlsx
+++ b/templates/21-cause-effect-fishbone.xlsx
@@ -298,10 +298,17 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1F4E79"/>
+            </a:solidFill>
             <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'Fishbone'!$A$38:$A$44</f>

--- a/templates/21-cause-effect-fishbone.xlsx
+++ b/templates/21-cause-effect-fishbone.xlsx
@@ -19,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="9">
     <font>
       <name val="Calibri"/>
@@ -147,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -177,6 +179,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -324,6 +327,40 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Mean — below this is a branch you are not looking at</v>
+          </tx>
+          <spPr>
+            <a:ln w="18000">
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Fishbone'!$H$38:$H$44</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -353,6 +390,9 @@
         <crossAx val="10"/>
       </valAx>
     </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -378,7 +418,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>9</col>
       <colOff>0</colOff>
       <row>7</row>
       <rowOff>0</rowOff>
@@ -1509,6 +1549,11 @@
       <c r="D37" s="7" t="n"/>
       <c r="E37" s="7" t="n"/>
       <c r="F37" s="7" t="n"/>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Mean causes per branch</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -1527,6 +1572,10 @@
       <c r="D38" s="16" t="n"/>
       <c r="E38" s="16" t="n"/>
       <c r="F38" s="16" t="n"/>
+      <c r="H38" s="17">
+        <f>AVERAGE($B$38:$B$44)</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -1545,6 +1594,10 @@
       <c r="D39" s="16" t="n"/>
       <c r="E39" s="16" t="n"/>
       <c r="F39" s="16" t="n"/>
+      <c r="H39" s="17">
+        <f>AVERAGE($B$38:$B$44)</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -1563,6 +1616,10 @@
       <c r="D40" s="16" t="n"/>
       <c r="E40" s="16" t="n"/>
       <c r="F40" s="16" t="n"/>
+      <c r="H40" s="17">
+        <f>AVERAGE($B$38:$B$44)</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -1581,6 +1638,10 @@
       <c r="D41" s="16" t="n"/>
       <c r="E41" s="16" t="n"/>
       <c r="F41" s="16" t="n"/>
+      <c r="H41" s="17">
+        <f>AVERAGE($B$38:$B$44)</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -1599,6 +1660,10 @@
       <c r="D42" s="16" t="n"/>
       <c r="E42" s="16" t="n"/>
       <c r="F42" s="16" t="n"/>
+      <c r="H42" s="17">
+        <f>AVERAGE($B$38:$B$44)</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -1617,6 +1682,10 @@
       <c r="D43" s="16" t="n"/>
       <c r="E43" s="16" t="n"/>
       <c r="F43" s="16" t="n"/>
+      <c r="H43" s="17">
+        <f>AVERAGE($B$38:$B$44)</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -1635,6 +1704,10 @@
       <c r="D44" s="16" t="n"/>
       <c r="E44" s="16" t="n"/>
       <c r="F44" s="16" t="n"/>
+      <c r="H44" s="17">
+        <f>AVERAGE($B$38:$B$44)</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -1762,274 +1835,274 @@
     </row>
     <row r="3"/>
     <row r="4" ht="20" customHeight="1">
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>People</t>
         </is>
       </c>
-      <c r="C4" s="18" t="n"/>
-      <c r="D4" s="18" t="n"/>
-      <c r="E4" s="18" t="n"/>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+      <c r="E4" s="19" t="n"/>
+      <c r="H4" s="18" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="I4" s="18" t="n"/>
-      <c r="J4" s="18" t="n"/>
-      <c r="K4" s="18" t="n"/>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="I4" s="19" t="n"/>
+      <c r="J4" s="19" t="n"/>
+      <c r="K4" s="19" t="n"/>
+      <c r="N4" s="18" t="inlineStr">
         <is>
           <t>Systems</t>
         </is>
       </c>
-      <c r="O4" s="18" t="n"/>
-      <c r="P4" s="18" t="n"/>
-      <c r="Q4" s="18" t="n"/>
-      <c r="T4" s="17" t="inlineStr">
+      <c r="O4" s="19" t="n"/>
+      <c r="P4" s="19" t="n"/>
+      <c r="Q4" s="19" t="n"/>
+      <c r="T4" s="18" t="inlineStr">
         <is>
           <t>Knowledge</t>
         </is>
       </c>
-      <c r="U4" s="18" t="n"/>
-      <c r="V4" s="18" t="n"/>
-      <c r="W4" s="18" t="n"/>
+      <c r="U4" s="19" t="n"/>
+      <c r="V4" s="19" t="n"/>
+      <c r="W4" s="19" t="n"/>
     </row>
     <row r="5">
-      <c r="F5" s="19" t="n"/>
-      <c r="L5" s="19" t="n"/>
-      <c r="R5" s="19" t="n"/>
-      <c r="X5" s="19" t="n"/>
+      <c r="F5" s="20" t="n"/>
+      <c r="L5" s="20" t="n"/>
+      <c r="R5" s="20" t="n"/>
+      <c r="X5" s="20" t="n"/>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="B6" s="20">
+      <c r="B6" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("People|1",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Process|1",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="N6" s="20">
+      <c r="N6" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Systems|1",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="T6" s="20">
+      <c r="T6" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Knowledge|1",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="7"/>
     <row r="8" ht="26" customHeight="1">
-      <c r="B8" s="20">
+      <c r="B8" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("People|2",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Process|2",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="N8" s="20">
+      <c r="N8" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Systems|2",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="T8" s="20">
+      <c r="T8" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Knowledge|2",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="9"/>
     <row r="10" ht="26" customHeight="1">
-      <c r="B10" s="20">
+      <c r="B10" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("People|3",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Process|3",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="N10" s="20">
+      <c r="N10" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Systems|3",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="T10" s="20">
+      <c r="T10" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Knowledge|3",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="11"/>
     <row r="12" ht="26" customHeight="1">
-      <c r="B12" s="20">
+      <c r="B12" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("People|4",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Process|4",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="N12" s="20">
+      <c r="N12" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Systems|4",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="T12" s="20">
+      <c r="T12" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Knowledge|4",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="AA12" s="21">
+      <c r="AA12" s="22">
         <f>Fishbone!B5</f>
         <v/>
       </c>
-      <c r="AB12" s="22" t="n"/>
-      <c r="AC12" s="22" t="n"/>
-      <c r="AD12" s="22" t="n"/>
+      <c r="AB12" s="23" t="n"/>
+      <c r="AC12" s="23" t="n"/>
+      <c r="AD12" s="23" t="n"/>
     </row>
     <row r="13">
-      <c r="AA13" s="22" t="n"/>
-      <c r="AB13" s="22" t="n"/>
-      <c r="AC13" s="22" t="n"/>
-      <c r="AD13" s="22" t="n"/>
+      <c r="AA13" s="23" t="n"/>
+      <c r="AB13" s="23" t="n"/>
+      <c r="AC13" s="23" t="n"/>
+      <c r="AD13" s="23" t="n"/>
     </row>
     <row r="14">
-      <c r="AA14" s="22" t="n"/>
-      <c r="AB14" s="22" t="n"/>
-      <c r="AC14" s="22" t="n"/>
-      <c r="AD14" s="22" t="n"/>
+      <c r="AA14" s="23" t="n"/>
+      <c r="AB14" s="23" t="n"/>
+      <c r="AC14" s="23" t="n"/>
+      <c r="AD14" s="23" t="n"/>
     </row>
     <row r="15" ht="10" customHeight="1">
-      <c r="B15" s="23" t="n"/>
-      <c r="C15" s="23" t="n"/>
-      <c r="D15" s="23" t="n"/>
-      <c r="E15" s="23" t="n"/>
-      <c r="F15" s="23" t="n"/>
-      <c r="G15" s="23" t="n"/>
-      <c r="H15" s="23" t="n"/>
-      <c r="I15" s="23" t="n"/>
-      <c r="J15" s="23" t="n"/>
-      <c r="K15" s="23" t="n"/>
-      <c r="L15" s="23" t="n"/>
-      <c r="M15" s="23" t="n"/>
-      <c r="N15" s="23" t="n"/>
-      <c r="O15" s="23" t="n"/>
-      <c r="P15" s="23" t="n"/>
-      <c r="Q15" s="23" t="n"/>
-      <c r="R15" s="23" t="n"/>
-      <c r="S15" s="23" t="n"/>
-      <c r="T15" s="23" t="n"/>
-      <c r="U15" s="23" t="n"/>
-      <c r="V15" s="23" t="n"/>
-      <c r="W15" s="23" t="n"/>
-      <c r="X15" s="23" t="n"/>
-      <c r="Y15" s="23" t="n"/>
-      <c r="Z15" s="23" t="n"/>
-      <c r="AA15" s="22" t="n"/>
-      <c r="AB15" s="22" t="n"/>
-      <c r="AC15" s="22" t="n"/>
-      <c r="AD15" s="22" t="n"/>
+      <c r="B15" s="24" t="n"/>
+      <c r="C15" s="24" t="n"/>
+      <c r="D15" s="24" t="n"/>
+      <c r="E15" s="24" t="n"/>
+      <c r="F15" s="24" t="n"/>
+      <c r="G15" s="24" t="n"/>
+      <c r="H15" s="24" t="n"/>
+      <c r="I15" s="24" t="n"/>
+      <c r="J15" s="24" t="n"/>
+      <c r="K15" s="24" t="n"/>
+      <c r="L15" s="24" t="n"/>
+      <c r="M15" s="24" t="n"/>
+      <c r="N15" s="24" t="n"/>
+      <c r="O15" s="24" t="n"/>
+      <c r="P15" s="24" t="n"/>
+      <c r="Q15" s="24" t="n"/>
+      <c r="R15" s="24" t="n"/>
+      <c r="S15" s="24" t="n"/>
+      <c r="T15" s="24" t="n"/>
+      <c r="U15" s="24" t="n"/>
+      <c r="V15" s="24" t="n"/>
+      <c r="W15" s="24" t="n"/>
+      <c r="X15" s="24" t="n"/>
+      <c r="Y15" s="24" t="n"/>
+      <c r="Z15" s="24" t="n"/>
+      <c r="AA15" s="23" t="n"/>
+      <c r="AB15" s="23" t="n"/>
+      <c r="AC15" s="23" t="n"/>
+      <c r="AD15" s="23" t="n"/>
     </row>
     <row r="16">
-      <c r="I16" s="24" t="n"/>
-      <c r="O16" s="24" t="n"/>
-      <c r="U16" s="24" t="n"/>
-      <c r="AA16" s="22" t="n"/>
-      <c r="AB16" s="22" t="n"/>
-      <c r="AC16" s="22" t="n"/>
-      <c r="AD16" s="22" t="n"/>
+      <c r="I16" s="25" t="n"/>
+      <c r="O16" s="25" t="n"/>
+      <c r="U16" s="25" t="n"/>
+      <c r="AA16" s="23" t="n"/>
+      <c r="AB16" s="23" t="n"/>
+      <c r="AC16" s="23" t="n"/>
+      <c r="AD16" s="23" t="n"/>
     </row>
     <row r="17">
-      <c r="AA17" s="22" t="n"/>
-      <c r="AB17" s="22" t="n"/>
-      <c r="AC17" s="22" t="n"/>
-      <c r="AD17" s="22" t="n"/>
+      <c r="AA17" s="23" t="n"/>
+      <c r="AB17" s="23" t="n"/>
+      <c r="AC17" s="23" t="n"/>
+      <c r="AD17" s="23" t="n"/>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="E18" s="20">
+      <c r="E18" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Routing &amp; demand|1",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="K18" s="20">
+      <c r="K18" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Product / upstream|1",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="Q18" s="20">
+      <c r="Q18" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Measurement|1",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="AA18" s="22" t="n"/>
-      <c r="AB18" s="22" t="n"/>
-      <c r="AC18" s="22" t="n"/>
-      <c r="AD18" s="22" t="n"/>
+      <c r="AA18" s="23" t="n"/>
+      <c r="AB18" s="23" t="n"/>
+      <c r="AC18" s="23" t="n"/>
+      <c r="AD18" s="23" t="n"/>
     </row>
     <row r="19"/>
     <row r="20" ht="26" customHeight="1">
-      <c r="E20" s="20">
+      <c r="E20" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Routing &amp; demand|2",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="K20" s="20">
+      <c r="K20" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Product / upstream|2",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="Q20" s="20">
+      <c r="Q20" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Measurement|2",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="21"/>
     <row r="22" ht="26" customHeight="1">
-      <c r="E22" s="20">
+      <c r="E22" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Routing &amp; demand|3",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="K22" s="20">
+      <c r="K22" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Product / upstream|3",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="Q22" s="20">
+      <c r="Q22" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Measurement|3",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="23"/>
     <row r="24" ht="26" customHeight="1">
-      <c r="E24" s="20">
+      <c r="E24" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Routing &amp; demand|4",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="K24" s="20">
+      <c r="K24" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Product / upstream|4",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="Q24" s="20">
+      <c r="Q24" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Measurement|4",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="25"/>
     <row r="26" ht="20" customHeight="1">
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="18" t="inlineStr">
         <is>
           <t>Routing &amp; demand</t>
         </is>
       </c>
-      <c r="F26" s="18" t="n"/>
-      <c r="G26" s="18" t="n"/>
-      <c r="H26" s="18" t="n"/>
-      <c r="K26" s="17" t="inlineStr">
+      <c r="F26" s="19" t="n"/>
+      <c r="G26" s="19" t="n"/>
+      <c r="H26" s="19" t="n"/>
+      <c r="K26" s="18" t="inlineStr">
         <is>
           <t>Product / upstream</t>
         </is>
       </c>
-      <c r="L26" s="18" t="n"/>
-      <c r="M26" s="18" t="n"/>
-      <c r="N26" s="18" t="n"/>
-      <c r="Q26" s="17" t="inlineStr">
+      <c r="L26" s="19" t="n"/>
+      <c r="M26" s="19" t="n"/>
+      <c r="N26" s="19" t="n"/>
+      <c r="Q26" s="18" t="inlineStr">
         <is>
           <t>Measurement</t>
         </is>
       </c>
-      <c r="R26" s="18" t="n"/>
-      <c r="S26" s="18" t="n"/>
-      <c r="T26" s="18" t="n"/>
+      <c r="R26" s="19" t="n"/>
+      <c r="S26" s="19" t="n"/>
+      <c r="T26" s="19" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2128,7 +2201,7 @@
           <t>People</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>Skill, tenure, authority limits, coaching, workload, incentive conflicts.</t>
         </is>
@@ -2140,7 +2213,7 @@
           <t>Process</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Steps that can be skipped, missing pending states, approvals, handoffs, queue discipline.</t>
         </is>
@@ -2152,7 +2225,7 @@
           <t>Systems</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Tooling gaps, swivel-chair work, latency, permissions, integrations that fail silently.</t>
         </is>
@@ -2164,7 +2237,7 @@
           <t>Knowledge</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Missing or wrong articles, search that does not find them, content nobody owns.</t>
         </is>
@@ -2176,7 +2249,7 @@
           <t>Routing &amp; demand</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Mis-routing, IVR options, skill-based routing rules, arrival patterns, mix shift.</t>
         </is>
@@ -2188,7 +2261,7 @@
           <t>Product / upstream</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>Defects reaching customers, confusing UX, billing logic, release cadence.</t>
         </is>
@@ -2200,7 +2273,7 @@
           <t>Measurement</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Disposition codes, QA rubric, operational definitions, instrumentation gaps.</t>
         </is>

--- a/templates/21-cause-effect-fishbone.xlsx
+++ b/templates/21-cause-effect-fishbone.xlsx
@@ -300,6 +300,9 @@
         <ser>
           <idx val="0"/>
           <order val="0"/>
+          <tx>
+            <v>Causes on this branch</v>
+          </tx>
           <spPr>
             <a:solidFill>
               <a:srgbClr val="1F4E79"/>

--- a/templates/21-cause-effect-fishbone.xlsx
+++ b/templates/21-cause-effect-fishbone.xlsx
@@ -421,9 +421,9 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>21</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2700000"/>
@@ -1541,6 +1541,7 @@
         <v/>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
@@ -1712,6 +1713,7 @@
         <v/>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>

--- a/templates/21-cause-effect-fishbone.xlsx
+++ b/templates/21-cause-effect-fishbone.xlsx
@@ -2109,6 +2109,7 @@
       <c r="S26" s="19" t="n"/>
       <c r="T26" s="19" t="n"/>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>

--- a/templates/21-cause-effect-fishbone.xlsx
+++ b/templates/21-cause-effect-fishbone.xlsx
@@ -772,14 +772,14 @@
     <row r="6">
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Green row</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
+          <t>Green cells</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>A worked example so you can see the expected format. Delete it when you start.</t>
+          <t>A worked example, so you can see the expected format and the charts say something the moment you open the file. Replace it with your own data when you start.</t>
         </is>
       </c>
     </row>

--- a/templates/21-cause-effect-fishbone.xlsx
+++ b/templates/21-cause-effect-fishbone.xlsx
@@ -149,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -170,14 +170,13 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1565,18 +1564,18 @@
           <t>People</t>
         </is>
       </c>
-      <c r="B38" s="15">
+      <c r="B38" s="12">
         <f>COUNTIF($A$8:$A$35,A38)</f>
         <v/>
       </c>
-      <c r="C38" s="15">
+      <c r="C38" s="12">
         <f>IF(COUNTIF($A$8:$A$35,A38)=0,"EMPTY — look again","")</f>
         <v/>
       </c>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
-      <c r="H38" s="17">
+      <c r="D38" s="15" t="n"/>
+      <c r="E38" s="15" t="n"/>
+      <c r="F38" s="15" t="n"/>
+      <c r="H38" s="16">
         <f>AVERAGE($B$38:$B$44)</f>
         <v/>
       </c>
@@ -1587,18 +1586,18 @@
           <t>Process</t>
         </is>
       </c>
-      <c r="B39" s="15">
+      <c r="B39" s="12">
         <f>COUNTIF($A$8:$A$35,A39)</f>
         <v/>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="12">
         <f>IF(COUNTIF($A$8:$A$35,A39)=0,"EMPTY — look again","")</f>
         <v/>
       </c>
-      <c r="D39" s="16" t="n"/>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n"/>
-      <c r="H39" s="17">
+      <c r="D39" s="15" t="n"/>
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="15" t="n"/>
+      <c r="H39" s="16">
         <f>AVERAGE($B$38:$B$44)</f>
         <v/>
       </c>
@@ -1609,18 +1608,18 @@
           <t>Systems</t>
         </is>
       </c>
-      <c r="B40" s="15">
+      <c r="B40" s="12">
         <f>COUNTIF($A$8:$A$35,A40)</f>
         <v/>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="12">
         <f>IF(COUNTIF($A$8:$A$35,A40)=0,"EMPTY — look again","")</f>
         <v/>
       </c>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
-      <c r="H40" s="17">
+      <c r="D40" s="15" t="n"/>
+      <c r="E40" s="15" t="n"/>
+      <c r="F40" s="15" t="n"/>
+      <c r="H40" s="16">
         <f>AVERAGE($B$38:$B$44)</f>
         <v/>
       </c>
@@ -1631,18 +1630,18 @@
           <t>Knowledge</t>
         </is>
       </c>
-      <c r="B41" s="15">
+      <c r="B41" s="12">
         <f>COUNTIF($A$8:$A$35,A41)</f>
         <v/>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="12">
         <f>IF(COUNTIF($A$8:$A$35,A41)=0,"EMPTY — look again","")</f>
         <v/>
       </c>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
-      <c r="H41" s="17">
+      <c r="D41" s="15" t="n"/>
+      <c r="E41" s="15" t="n"/>
+      <c r="F41" s="15" t="n"/>
+      <c r="H41" s="16">
         <f>AVERAGE($B$38:$B$44)</f>
         <v/>
       </c>
@@ -1653,18 +1652,18 @@
           <t>Routing &amp; demand</t>
         </is>
       </c>
-      <c r="B42" s="15">
+      <c r="B42" s="12">
         <f>COUNTIF($A$8:$A$35,A42)</f>
         <v/>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="12">
         <f>IF(COUNTIF($A$8:$A$35,A42)=0,"EMPTY — look again","")</f>
         <v/>
       </c>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
-      <c r="H42" s="17">
+      <c r="D42" s="15" t="n"/>
+      <c r="E42" s="15" t="n"/>
+      <c r="F42" s="15" t="n"/>
+      <c r="H42" s="16">
         <f>AVERAGE($B$38:$B$44)</f>
         <v/>
       </c>
@@ -1675,18 +1674,18 @@
           <t>Product / upstream</t>
         </is>
       </c>
-      <c r="B43" s="15">
+      <c r="B43" s="12">
         <f>COUNTIF($A$8:$A$35,A43)</f>
         <v/>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="12">
         <f>IF(COUNTIF($A$8:$A$35,A43)=0,"EMPTY — look again","")</f>
         <v/>
       </c>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
-      <c r="H43" s="17">
+      <c r="D43" s="15" t="n"/>
+      <c r="E43" s="15" t="n"/>
+      <c r="F43" s="15" t="n"/>
+      <c r="H43" s="16">
         <f>AVERAGE($B$38:$B$44)</f>
         <v/>
       </c>
@@ -1697,18 +1696,18 @@
           <t>Measurement</t>
         </is>
       </c>
-      <c r="B44" s="15">
+      <c r="B44" s="12">
         <f>COUNTIF($A$8:$A$35,A44)</f>
         <v/>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="12">
         <f>IF(COUNTIF($A$8:$A$35,A44)=0,"EMPTY — look again","")</f>
         <v/>
       </c>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
-      <c r="H44" s="17">
+      <c r="D44" s="15" t="n"/>
+      <c r="E44" s="15" t="n"/>
+      <c r="F44" s="15" t="n"/>
+      <c r="H44" s="16">
         <f>AVERAGE($B$38:$B$44)</f>
         <v/>
       </c>
@@ -1840,274 +1839,274 @@
     </row>
     <row r="3"/>
     <row r="4" ht="20" customHeight="1">
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>People</t>
         </is>
       </c>
-      <c r="C4" s="19" t="n"/>
-      <c r="D4" s="19" t="n"/>
-      <c r="E4" s="19" t="n"/>
-      <c r="H4" s="18" t="inlineStr">
+      <c r="C4" s="18" t="n"/>
+      <c r="D4" s="18" t="n"/>
+      <c r="E4" s="18" t="n"/>
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="I4" s="19" t="n"/>
-      <c r="J4" s="19" t="n"/>
-      <c r="K4" s="19" t="n"/>
-      <c r="N4" s="18" t="inlineStr">
+      <c r="I4" s="18" t="n"/>
+      <c r="J4" s="18" t="n"/>
+      <c r="K4" s="18" t="n"/>
+      <c r="N4" s="17" t="inlineStr">
         <is>
           <t>Systems</t>
         </is>
       </c>
-      <c r="O4" s="19" t="n"/>
-      <c r="P4" s="19" t="n"/>
-      <c r="Q4" s="19" t="n"/>
-      <c r="T4" s="18" t="inlineStr">
+      <c r="O4" s="18" t="n"/>
+      <c r="P4" s="18" t="n"/>
+      <c r="Q4" s="18" t="n"/>
+      <c r="T4" s="17" t="inlineStr">
         <is>
           <t>Knowledge</t>
         </is>
       </c>
-      <c r="U4" s="19" t="n"/>
-      <c r="V4" s="19" t="n"/>
-      <c r="W4" s="19" t="n"/>
+      <c r="U4" s="18" t="n"/>
+      <c r="V4" s="18" t="n"/>
+      <c r="W4" s="18" t="n"/>
     </row>
     <row r="5">
-      <c r="F5" s="20" t="n"/>
-      <c r="L5" s="20" t="n"/>
-      <c r="R5" s="20" t="n"/>
-      <c r="X5" s="20" t="n"/>
+      <c r="F5" s="19" t="n"/>
+      <c r="L5" s="19" t="n"/>
+      <c r="R5" s="19" t="n"/>
+      <c r="X5" s="19" t="n"/>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="B6" s="21">
+      <c r="B6" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("People|1",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="H6" s="21">
+      <c r="H6" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Process|1",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="N6" s="21">
+      <c r="N6" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Systems|1",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="T6" s="21">
+      <c r="T6" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Knowledge|1",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="7"/>
     <row r="8" ht="26" customHeight="1">
-      <c r="B8" s="21">
+      <c r="B8" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("People|2",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="H8" s="21">
+      <c r="H8" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Process|2",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="N8" s="21">
+      <c r="N8" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Systems|2",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="T8" s="21">
+      <c r="T8" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Knowledge|2",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="9"/>
     <row r="10" ht="26" customHeight="1">
-      <c r="B10" s="21">
+      <c r="B10" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("People|3",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="H10" s="21">
+      <c r="H10" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Process|3",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="N10" s="21">
+      <c r="N10" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Systems|3",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="T10" s="21">
+      <c r="T10" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Knowledge|3",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="11"/>
     <row r="12" ht="26" customHeight="1">
-      <c r="B12" s="21">
+      <c r="B12" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("People|4",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Process|4",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="N12" s="21">
+      <c r="N12" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Systems|4",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="T12" s="21">
+      <c r="T12" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Knowledge|4",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="AA12" s="22">
+      <c r="AA12" s="21">
         <f>Fishbone!B5</f>
         <v/>
       </c>
-      <c r="AB12" s="23" t="n"/>
-      <c r="AC12" s="23" t="n"/>
-      <c r="AD12" s="23" t="n"/>
+      <c r="AB12" s="22" t="n"/>
+      <c r="AC12" s="22" t="n"/>
+      <c r="AD12" s="22" t="n"/>
     </row>
     <row r="13">
-      <c r="AA13" s="23" t="n"/>
-      <c r="AB13" s="23" t="n"/>
-      <c r="AC13" s="23" t="n"/>
-      <c r="AD13" s="23" t="n"/>
+      <c r="AA13" s="22" t="n"/>
+      <c r="AB13" s="22" t="n"/>
+      <c r="AC13" s="22" t="n"/>
+      <c r="AD13" s="22" t="n"/>
     </row>
     <row r="14">
-      <c r="AA14" s="23" t="n"/>
-      <c r="AB14" s="23" t="n"/>
-      <c r="AC14" s="23" t="n"/>
-      <c r="AD14" s="23" t="n"/>
+      <c r="AA14" s="22" t="n"/>
+      <c r="AB14" s="22" t="n"/>
+      <c r="AC14" s="22" t="n"/>
+      <c r="AD14" s="22" t="n"/>
     </row>
     <row r="15" ht="10" customHeight="1">
-      <c r="B15" s="24" t="n"/>
-      <c r="C15" s="24" t="n"/>
-      <c r="D15" s="24" t="n"/>
-      <c r="E15" s="24" t="n"/>
-      <c r="F15" s="24" t="n"/>
-      <c r="G15" s="24" t="n"/>
-      <c r="H15" s="24" t="n"/>
-      <c r="I15" s="24" t="n"/>
-      <c r="J15" s="24" t="n"/>
-      <c r="K15" s="24" t="n"/>
-      <c r="L15" s="24" t="n"/>
-      <c r="M15" s="24" t="n"/>
-      <c r="N15" s="24" t="n"/>
-      <c r="O15" s="24" t="n"/>
-      <c r="P15" s="24" t="n"/>
-      <c r="Q15" s="24" t="n"/>
-      <c r="R15" s="24" t="n"/>
-      <c r="S15" s="24" t="n"/>
-      <c r="T15" s="24" t="n"/>
-      <c r="U15" s="24" t="n"/>
-      <c r="V15" s="24" t="n"/>
-      <c r="W15" s="24" t="n"/>
-      <c r="X15" s="24" t="n"/>
-      <c r="Y15" s="24" t="n"/>
-      <c r="Z15" s="24" t="n"/>
-      <c r="AA15" s="23" t="n"/>
-      <c r="AB15" s="23" t="n"/>
-      <c r="AC15" s="23" t="n"/>
-      <c r="AD15" s="23" t="n"/>
+      <c r="B15" s="23" t="n"/>
+      <c r="C15" s="23" t="n"/>
+      <c r="D15" s="23" t="n"/>
+      <c r="E15" s="23" t="n"/>
+      <c r="F15" s="23" t="n"/>
+      <c r="G15" s="23" t="n"/>
+      <c r="H15" s="23" t="n"/>
+      <c r="I15" s="23" t="n"/>
+      <c r="J15" s="23" t="n"/>
+      <c r="K15" s="23" t="n"/>
+      <c r="L15" s="23" t="n"/>
+      <c r="M15" s="23" t="n"/>
+      <c r="N15" s="23" t="n"/>
+      <c r="O15" s="23" t="n"/>
+      <c r="P15" s="23" t="n"/>
+      <c r="Q15" s="23" t="n"/>
+      <c r="R15" s="23" t="n"/>
+      <c r="S15" s="23" t="n"/>
+      <c r="T15" s="23" t="n"/>
+      <c r="U15" s="23" t="n"/>
+      <c r="V15" s="23" t="n"/>
+      <c r="W15" s="23" t="n"/>
+      <c r="X15" s="23" t="n"/>
+      <c r="Y15" s="23" t="n"/>
+      <c r="Z15" s="23" t="n"/>
+      <c r="AA15" s="22" t="n"/>
+      <c r="AB15" s="22" t="n"/>
+      <c r="AC15" s="22" t="n"/>
+      <c r="AD15" s="22" t="n"/>
     </row>
     <row r="16">
-      <c r="I16" s="25" t="n"/>
-      <c r="O16" s="25" t="n"/>
-      <c r="U16" s="25" t="n"/>
-      <c r="AA16" s="23" t="n"/>
-      <c r="AB16" s="23" t="n"/>
-      <c r="AC16" s="23" t="n"/>
-      <c r="AD16" s="23" t="n"/>
+      <c r="I16" s="24" t="n"/>
+      <c r="O16" s="24" t="n"/>
+      <c r="U16" s="24" t="n"/>
+      <c r="AA16" s="22" t="n"/>
+      <c r="AB16" s="22" t="n"/>
+      <c r="AC16" s="22" t="n"/>
+      <c r="AD16" s="22" t="n"/>
     </row>
     <row r="17">
-      <c r="AA17" s="23" t="n"/>
-      <c r="AB17" s="23" t="n"/>
-      <c r="AC17" s="23" t="n"/>
-      <c r="AD17" s="23" t="n"/>
+      <c r="AA17" s="22" t="n"/>
+      <c r="AB17" s="22" t="n"/>
+      <c r="AC17" s="22" t="n"/>
+      <c r="AD17" s="22" t="n"/>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="E18" s="21">
+      <c r="E18" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Routing &amp; demand|1",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="K18" s="21">
+      <c r="K18" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Product / upstream|1",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="Q18" s="21">
+      <c r="Q18" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Measurement|1",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="AA18" s="23" t="n"/>
-      <c r="AB18" s="23" t="n"/>
-      <c r="AC18" s="23" t="n"/>
-      <c r="AD18" s="23" t="n"/>
+      <c r="AA18" s="22" t="n"/>
+      <c r="AB18" s="22" t="n"/>
+      <c r="AC18" s="22" t="n"/>
+      <c r="AD18" s="22" t="n"/>
     </row>
     <row r="19"/>
     <row r="20" ht="26" customHeight="1">
-      <c r="E20" s="21">
+      <c r="E20" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Routing &amp; demand|2",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="K20" s="21">
+      <c r="K20" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Product / upstream|2",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="Q20" s="21">
+      <c r="Q20" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Measurement|2",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="21"/>
     <row r="22" ht="26" customHeight="1">
-      <c r="E22" s="21">
+      <c r="E22" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Routing &amp; demand|3",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="K22" s="21">
+      <c r="K22" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Product / upstream|3",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="Q22" s="21">
+      <c r="Q22" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Measurement|3",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="23"/>
     <row r="24" ht="26" customHeight="1">
-      <c r="E24" s="21">
+      <c r="E24" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Routing &amp; demand|4",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="K24" s="21">
+      <c r="K24" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Product / upstream|4",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="Q24" s="21">
+      <c r="Q24" s="20">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Measurement|4",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="25"/>
     <row r="26" ht="20" customHeight="1">
-      <c r="E26" s="18" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>Routing &amp; demand</t>
         </is>
       </c>
-      <c r="F26" s="19" t="n"/>
-      <c r="G26" s="19" t="n"/>
-      <c r="H26" s="19" t="n"/>
-      <c r="K26" s="18" t="inlineStr">
+      <c r="F26" s="18" t="n"/>
+      <c r="G26" s="18" t="n"/>
+      <c r="H26" s="18" t="n"/>
+      <c r="K26" s="17" t="inlineStr">
         <is>
           <t>Product / upstream</t>
         </is>
       </c>
-      <c r="L26" s="19" t="n"/>
-      <c r="M26" s="19" t="n"/>
-      <c r="N26" s="19" t="n"/>
-      <c r="Q26" s="18" t="inlineStr">
+      <c r="L26" s="18" t="n"/>
+      <c r="M26" s="18" t="n"/>
+      <c r="N26" s="18" t="n"/>
+      <c r="Q26" s="17" t="inlineStr">
         <is>
           <t>Measurement</t>
         </is>
       </c>
-      <c r="R26" s="19" t="n"/>
-      <c r="S26" s="19" t="n"/>
-      <c r="T26" s="19" t="n"/>
+      <c r="R26" s="18" t="n"/>
+      <c r="S26" s="18" t="n"/>
+      <c r="T26" s="18" t="n"/>
     </row>
     <row r="27"/>
     <row r="28">
@@ -2207,7 +2206,7 @@
           <t>People</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Skill, tenure, authority limits, coaching, workload, incentive conflicts.</t>
         </is>
@@ -2219,7 +2218,7 @@
           <t>Process</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Steps that can be skipped, missing pending states, approvals, handoffs, queue discipline.</t>
         </is>
@@ -2231,7 +2230,7 @@
           <t>Systems</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Tooling gaps, swivel-chair work, latency, permissions, integrations that fail silently.</t>
         </is>
@@ -2243,7 +2242,7 @@
           <t>Knowledge</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Missing or wrong articles, search that does not find them, content nobody owns.</t>
         </is>
@@ -2255,7 +2254,7 @@
           <t>Routing &amp; demand</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Mis-routing, IVR options, skill-based routing rules, arrival patterns, mix shift.</t>
         </is>
@@ -2267,7 +2266,7 @@
           <t>Product / upstream</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Defects reaching customers, confusing UX, billing logic, release cadence.</t>
         </is>
@@ -2279,7 +2278,7 @@
           <t>Measurement</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Disposition codes, QA rubric, operational definitions, instrumentation gaps.</t>
         </is>

--- a/templates/21-cause-effect-fishbone.xlsx
+++ b/templates/21-cause-effect-fishbone.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,6 +63,11 @@
     </font>
     <font>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF4B5563"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="9">
@@ -149,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -175,6 +180,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -891,6 +899,15 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
     <col hidden="1" width="22" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
@@ -1375,7 +1392,7 @@
         <v/>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="66" customHeight="1">
       <c r="A25" s="13" t="n"/>
       <c r="B25" s="13" t="n"/>
       <c r="C25" s="13" t="n"/>
@@ -1385,6 +1402,12 @@
         <v/>
       </c>
       <c r="F25" s="13" t="n"/>
+      <c r="J25" s="15" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  This counts causes, not their importance. A branch with one cause usually means the team ran out of ideas there, not that the branch is clean — Measurement and Environment are the two that go thin in support. Fill the thin branches before you start scoring anything.
+SO:  Go back to the thin branches before scoring anything. A branch with one cause is a question nobody asked, and scoring the chart as it stands ranks the branches you happened to think hardest about.</t>
+        </is>
+      </c>
       <c r="T25" s="5">
         <f>IF(A25="","",A25&amp;"|"&amp;COUNTIF($A$8:A25,A25))</f>
         <v/>
@@ -1572,10 +1595,10 @@
         <f>IF(COUNTIF($A$8:$A$35,A38)=0,"EMPTY — look again","")</f>
         <v/>
       </c>
-      <c r="D38" s="15" t="n"/>
-      <c r="E38" s="15" t="n"/>
-      <c r="F38" s="15" t="n"/>
-      <c r="H38" s="16">
+      <c r="D38" s="16" t="n"/>
+      <c r="E38" s="16" t="n"/>
+      <c r="F38" s="16" t="n"/>
+      <c r="H38" s="17">
         <f>AVERAGE($B$38:$B$44)</f>
         <v/>
       </c>
@@ -1594,10 +1617,10 @@
         <f>IF(COUNTIF($A$8:$A$35,A39)=0,"EMPTY — look again","")</f>
         <v/>
       </c>
-      <c r="D39" s="15" t="n"/>
-      <c r="E39" s="15" t="n"/>
-      <c r="F39" s="15" t="n"/>
-      <c r="H39" s="16">
+      <c r="D39" s="16" t="n"/>
+      <c r="E39" s="16" t="n"/>
+      <c r="F39" s="16" t="n"/>
+      <c r="H39" s="17">
         <f>AVERAGE($B$38:$B$44)</f>
         <v/>
       </c>
@@ -1616,10 +1639,10 @@
         <f>IF(COUNTIF($A$8:$A$35,A40)=0,"EMPTY — look again","")</f>
         <v/>
       </c>
-      <c r="D40" s="15" t="n"/>
-      <c r="E40" s="15" t="n"/>
-      <c r="F40" s="15" t="n"/>
-      <c r="H40" s="16">
+      <c r="D40" s="16" t="n"/>
+      <c r="E40" s="16" t="n"/>
+      <c r="F40" s="16" t="n"/>
+      <c r="H40" s="17">
         <f>AVERAGE($B$38:$B$44)</f>
         <v/>
       </c>
@@ -1638,10 +1661,10 @@
         <f>IF(COUNTIF($A$8:$A$35,A41)=0,"EMPTY — look again","")</f>
         <v/>
       </c>
-      <c r="D41" s="15" t="n"/>
-      <c r="E41" s="15" t="n"/>
-      <c r="F41" s="15" t="n"/>
-      <c r="H41" s="16">
+      <c r="D41" s="16" t="n"/>
+      <c r="E41" s="16" t="n"/>
+      <c r="F41" s="16" t="n"/>
+      <c r="H41" s="17">
         <f>AVERAGE($B$38:$B$44)</f>
         <v/>
       </c>
@@ -1660,10 +1683,10 @@
         <f>IF(COUNTIF($A$8:$A$35,A42)=0,"EMPTY — look again","")</f>
         <v/>
       </c>
-      <c r="D42" s="15" t="n"/>
-      <c r="E42" s="15" t="n"/>
-      <c r="F42" s="15" t="n"/>
-      <c r="H42" s="16">
+      <c r="D42" s="16" t="n"/>
+      <c r="E42" s="16" t="n"/>
+      <c r="F42" s="16" t="n"/>
+      <c r="H42" s="17">
         <f>AVERAGE($B$38:$B$44)</f>
         <v/>
       </c>
@@ -1682,10 +1705,10 @@
         <f>IF(COUNTIF($A$8:$A$35,A43)=0,"EMPTY — look again","")</f>
         <v/>
       </c>
-      <c r="D43" s="15" t="n"/>
-      <c r="E43" s="15" t="n"/>
-      <c r="F43" s="15" t="n"/>
-      <c r="H43" s="16">
+      <c r="D43" s="16" t="n"/>
+      <c r="E43" s="16" t="n"/>
+      <c r="F43" s="16" t="n"/>
+      <c r="H43" s="17">
         <f>AVERAGE($B$38:$B$44)</f>
         <v/>
       </c>
@@ -1704,10 +1727,10 @@
         <f>IF(COUNTIF($A$8:$A$35,A44)=0,"EMPTY — look again","")</f>
         <v/>
       </c>
-      <c r="D44" s="15" t="n"/>
-      <c r="E44" s="15" t="n"/>
-      <c r="F44" s="15" t="n"/>
-      <c r="H44" s="16">
+      <c r="D44" s="16" t="n"/>
+      <c r="E44" s="16" t="n"/>
+      <c r="F44" s="16" t="n"/>
+      <c r="H44" s="17">
         <f>AVERAGE($B$38:$B$44)</f>
         <v/>
       </c>
@@ -1721,11 +1744,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C40:F40"/>
     <mergeCell ref="A46:F46"/>
     <mergeCell ref="C39:F39"/>
+    <mergeCell ref="J25:R25"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="C43:F43"/>
@@ -1839,274 +1863,274 @@
     </row>
     <row r="3"/>
     <row r="4" ht="20" customHeight="1">
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>People</t>
         </is>
       </c>
-      <c r="C4" s="18" t="n"/>
-      <c r="D4" s="18" t="n"/>
-      <c r="E4" s="18" t="n"/>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+      <c r="E4" s="19" t="n"/>
+      <c r="H4" s="18" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="I4" s="18" t="n"/>
-      <c r="J4" s="18" t="n"/>
-      <c r="K4" s="18" t="n"/>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="I4" s="19" t="n"/>
+      <c r="J4" s="19" t="n"/>
+      <c r="K4" s="19" t="n"/>
+      <c r="N4" s="18" t="inlineStr">
         <is>
           <t>Systems</t>
         </is>
       </c>
-      <c r="O4" s="18" t="n"/>
-      <c r="P4" s="18" t="n"/>
-      <c r="Q4" s="18" t="n"/>
-      <c r="T4" s="17" t="inlineStr">
+      <c r="O4" s="19" t="n"/>
+      <c r="P4" s="19" t="n"/>
+      <c r="Q4" s="19" t="n"/>
+      <c r="T4" s="18" t="inlineStr">
         <is>
           <t>Knowledge</t>
         </is>
       </c>
-      <c r="U4" s="18" t="n"/>
-      <c r="V4" s="18" t="n"/>
-      <c r="W4" s="18" t="n"/>
+      <c r="U4" s="19" t="n"/>
+      <c r="V4" s="19" t="n"/>
+      <c r="W4" s="19" t="n"/>
     </row>
     <row r="5">
-      <c r="F5" s="19" t="n"/>
-      <c r="L5" s="19" t="n"/>
-      <c r="R5" s="19" t="n"/>
-      <c r="X5" s="19" t="n"/>
+      <c r="F5" s="20" t="n"/>
+      <c r="L5" s="20" t="n"/>
+      <c r="R5" s="20" t="n"/>
+      <c r="X5" s="20" t="n"/>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="B6" s="20">
+      <c r="B6" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("People|1",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Process|1",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="N6" s="20">
+      <c r="N6" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Systems|1",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="T6" s="20">
+      <c r="T6" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Knowledge|1",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="7"/>
     <row r="8" ht="26" customHeight="1">
-      <c r="B8" s="20">
+      <c r="B8" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("People|2",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Process|2",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="N8" s="20">
+      <c r="N8" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Systems|2",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="T8" s="20">
+      <c r="T8" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Knowledge|2",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="9"/>
     <row r="10" ht="26" customHeight="1">
-      <c r="B10" s="20">
+      <c r="B10" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("People|3",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Process|3",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="N10" s="20">
+      <c r="N10" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Systems|3",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="T10" s="20">
+      <c r="T10" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Knowledge|3",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="11"/>
     <row r="12" ht="26" customHeight="1">
-      <c r="B12" s="20">
+      <c r="B12" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("People|4",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Process|4",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="N12" s="20">
+      <c r="N12" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Systems|4",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="T12" s="20">
+      <c r="T12" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Knowledge|4",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="AA12" s="21">
+      <c r="AA12" s="22">
         <f>Fishbone!B5</f>
         <v/>
       </c>
-      <c r="AB12" s="22" t="n"/>
-      <c r="AC12" s="22" t="n"/>
-      <c r="AD12" s="22" t="n"/>
+      <c r="AB12" s="23" t="n"/>
+      <c r="AC12" s="23" t="n"/>
+      <c r="AD12" s="23" t="n"/>
     </row>
     <row r="13">
-      <c r="AA13" s="22" t="n"/>
-      <c r="AB13" s="22" t="n"/>
-      <c r="AC13" s="22" t="n"/>
-      <c r="AD13" s="22" t="n"/>
+      <c r="AA13" s="23" t="n"/>
+      <c r="AB13" s="23" t="n"/>
+      <c r="AC13" s="23" t="n"/>
+      <c r="AD13" s="23" t="n"/>
     </row>
     <row r="14">
-      <c r="AA14" s="22" t="n"/>
-      <c r="AB14" s="22" t="n"/>
-      <c r="AC14" s="22" t="n"/>
-      <c r="AD14" s="22" t="n"/>
+      <c r="AA14" s="23" t="n"/>
+      <c r="AB14" s="23" t="n"/>
+      <c r="AC14" s="23" t="n"/>
+      <c r="AD14" s="23" t="n"/>
     </row>
     <row r="15" ht="10" customHeight="1">
-      <c r="B15" s="23" t="n"/>
-      <c r="C15" s="23" t="n"/>
-      <c r="D15" s="23" t="n"/>
-      <c r="E15" s="23" t="n"/>
-      <c r="F15" s="23" t="n"/>
-      <c r="G15" s="23" t="n"/>
-      <c r="H15" s="23" t="n"/>
-      <c r="I15" s="23" t="n"/>
-      <c r="J15" s="23" t="n"/>
-      <c r="K15" s="23" t="n"/>
-      <c r="L15" s="23" t="n"/>
-      <c r="M15" s="23" t="n"/>
-      <c r="N15" s="23" t="n"/>
-      <c r="O15" s="23" t="n"/>
-      <c r="P15" s="23" t="n"/>
-      <c r="Q15" s="23" t="n"/>
-      <c r="R15" s="23" t="n"/>
-      <c r="S15" s="23" t="n"/>
-      <c r="T15" s="23" t="n"/>
-      <c r="U15" s="23" t="n"/>
-      <c r="V15" s="23" t="n"/>
-      <c r="W15" s="23" t="n"/>
-      <c r="X15" s="23" t="n"/>
-      <c r="Y15" s="23" t="n"/>
-      <c r="Z15" s="23" t="n"/>
-      <c r="AA15" s="22" t="n"/>
-      <c r="AB15" s="22" t="n"/>
-      <c r="AC15" s="22" t="n"/>
-      <c r="AD15" s="22" t="n"/>
+      <c r="B15" s="24" t="n"/>
+      <c r="C15" s="24" t="n"/>
+      <c r="D15" s="24" t="n"/>
+      <c r="E15" s="24" t="n"/>
+      <c r="F15" s="24" t="n"/>
+      <c r="G15" s="24" t="n"/>
+      <c r="H15" s="24" t="n"/>
+      <c r="I15" s="24" t="n"/>
+      <c r="J15" s="24" t="n"/>
+      <c r="K15" s="24" t="n"/>
+      <c r="L15" s="24" t="n"/>
+      <c r="M15" s="24" t="n"/>
+      <c r="N15" s="24" t="n"/>
+      <c r="O15" s="24" t="n"/>
+      <c r="P15" s="24" t="n"/>
+      <c r="Q15" s="24" t="n"/>
+      <c r="R15" s="24" t="n"/>
+      <c r="S15" s="24" t="n"/>
+      <c r="T15" s="24" t="n"/>
+      <c r="U15" s="24" t="n"/>
+      <c r="V15" s="24" t="n"/>
+      <c r="W15" s="24" t="n"/>
+      <c r="X15" s="24" t="n"/>
+      <c r="Y15" s="24" t="n"/>
+      <c r="Z15" s="24" t="n"/>
+      <c r="AA15" s="23" t="n"/>
+      <c r="AB15" s="23" t="n"/>
+      <c r="AC15" s="23" t="n"/>
+      <c r="AD15" s="23" t="n"/>
     </row>
     <row r="16">
-      <c r="I16" s="24" t="n"/>
-      <c r="O16" s="24" t="n"/>
-      <c r="U16" s="24" t="n"/>
-      <c r="AA16" s="22" t="n"/>
-      <c r="AB16" s="22" t="n"/>
-      <c r="AC16" s="22" t="n"/>
-      <c r="AD16" s="22" t="n"/>
+      <c r="I16" s="25" t="n"/>
+      <c r="O16" s="25" t="n"/>
+      <c r="U16" s="25" t="n"/>
+      <c r="AA16" s="23" t="n"/>
+      <c r="AB16" s="23" t="n"/>
+      <c r="AC16" s="23" t="n"/>
+      <c r="AD16" s="23" t="n"/>
     </row>
     <row r="17">
-      <c r="AA17" s="22" t="n"/>
-      <c r="AB17" s="22" t="n"/>
-      <c r="AC17" s="22" t="n"/>
-      <c r="AD17" s="22" t="n"/>
+      <c r="AA17" s="23" t="n"/>
+      <c r="AB17" s="23" t="n"/>
+      <c r="AC17" s="23" t="n"/>
+      <c r="AD17" s="23" t="n"/>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="E18" s="20">
+      <c r="E18" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Routing &amp; demand|1",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="K18" s="20">
+      <c r="K18" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Product / upstream|1",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="Q18" s="20">
+      <c r="Q18" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Measurement|1",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="AA18" s="22" t="n"/>
-      <c r="AB18" s="22" t="n"/>
-      <c r="AC18" s="22" t="n"/>
-      <c r="AD18" s="22" t="n"/>
+      <c r="AA18" s="23" t="n"/>
+      <c r="AB18" s="23" t="n"/>
+      <c r="AC18" s="23" t="n"/>
+      <c r="AD18" s="23" t="n"/>
     </row>
     <row r="19"/>
     <row r="20" ht="26" customHeight="1">
-      <c r="E20" s="20">
+      <c r="E20" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Routing &amp; demand|2",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="K20" s="20">
+      <c r="K20" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Product / upstream|2",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="Q20" s="20">
+      <c r="Q20" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Measurement|2",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="21"/>
     <row r="22" ht="26" customHeight="1">
-      <c r="E22" s="20">
+      <c r="E22" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Routing &amp; demand|3",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="K22" s="20">
+      <c r="K22" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Product / upstream|3",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="Q22" s="20">
+      <c r="Q22" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Measurement|3",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="23"/>
     <row r="24" ht="26" customHeight="1">
-      <c r="E24" s="20">
+      <c r="E24" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Routing &amp; demand|4",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="K24" s="20">
+      <c r="K24" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Product / upstream|4",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
-      <c r="Q24" s="20">
+      <c r="Q24" s="21">
         <f>IFERROR(INDEX(Fishbone!$B$8:$B$35,MATCH("Measurement|4",Fishbone!$T$8:$T$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="25"/>
     <row r="26" ht="20" customHeight="1">
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="18" t="inlineStr">
         <is>
           <t>Routing &amp; demand</t>
         </is>
       </c>
-      <c r="F26" s="18" t="n"/>
-      <c r="G26" s="18" t="n"/>
-      <c r="H26" s="18" t="n"/>
-      <c r="K26" s="17" t="inlineStr">
+      <c r="F26" s="19" t="n"/>
+      <c r="G26" s="19" t="n"/>
+      <c r="H26" s="19" t="n"/>
+      <c r="K26" s="18" t="inlineStr">
         <is>
           <t>Product / upstream</t>
         </is>
       </c>
-      <c r="L26" s="18" t="n"/>
-      <c r="M26" s="18" t="n"/>
-      <c r="N26" s="18" t="n"/>
-      <c r="Q26" s="17" t="inlineStr">
+      <c r="L26" s="19" t="n"/>
+      <c r="M26" s="19" t="n"/>
+      <c r="N26" s="19" t="n"/>
+      <c r="Q26" s="18" t="inlineStr">
         <is>
           <t>Measurement</t>
         </is>
       </c>
-      <c r="R26" s="18" t="n"/>
-      <c r="S26" s="18" t="n"/>
-      <c r="T26" s="18" t="n"/>
+      <c r="R26" s="19" t="n"/>
+      <c r="S26" s="19" t="n"/>
+      <c r="T26" s="19" t="n"/>
     </row>
     <row r="27"/>
     <row r="28">
@@ -2206,7 +2230,7 @@
           <t>People</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>Skill, tenure, authority limits, coaching, workload, incentive conflicts.</t>
         </is>
@@ -2218,7 +2242,7 @@
           <t>Process</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Steps that can be skipped, missing pending states, approvals, handoffs, queue discipline.</t>
         </is>
@@ -2230,7 +2254,7 @@
           <t>Systems</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Tooling gaps, swivel-chair work, latency, permissions, integrations that fail silently.</t>
         </is>
@@ -2242,7 +2266,7 @@
           <t>Knowledge</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Missing or wrong articles, search that does not find them, content nobody owns.</t>
         </is>
@@ -2254,7 +2278,7 @@
           <t>Routing &amp; demand</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Mis-routing, IVR options, skill-based routing rules, arrival patterns, mix shift.</t>
         </is>
@@ -2266,7 +2290,7 @@
           <t>Product / upstream</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>Defects reaching customers, confusing UX, billing logic, release cadence.</t>
         </is>
@@ -2278,7 +2302,7 @@
           <t>Measurement</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Disposition codes, QA rubric, operational definitions, instrumentation gaps.</t>
         </is>
